--- a/V3/processed_data/20251011_additives_all_V2.xlsx
+++ b/V3/processed_data/20251011_additives_all_V2.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10704\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942A99D0-3A85-4807-98CF-14C05BC735C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD6D43F-0611-4541-9FF1-7F987B955CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$196</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5400" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="1544">
   <si>
     <t>comments</t>
   </si>
@@ -5135,24 +5138,6 @@
   <si>
     <t>B(F)(F)F.N1=CC=CC=C1; F[B-](F)(F)[N+]1=CC=[N+]([B-](F)(F)F)C=C1</t>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>B(F)(F)F.BY 2D=CC=CC=E3; F[B-](F)(F)[N+]3=CC=[N+]([B-](F)(F)F)E=E3</t>
-  </si>
-  <si>
-    <t>B(F)(F)F.OXIDE)-LITFSI=CC=CC=L5; F[B-](F)(F)[N+]5=CC=[N+]([B-](F)(F)F)L=L5</t>
-  </si>
-  <si>
-    <t>B(F)(F)F.FOR=CC=CC=B4; F[B-](F)(F)[L+]4=CC=[L+]([B-](F)(F)F)B=B4</t>
-  </si>
-  <si>
-    <t>B(F)(F)F.THERMAL STABILITY=CC=CC=B4; F[B-](F)(F)[L+]4=CC=[L+]([B-](F)(F)F)B=B4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B(F)(F)F.LITHIUM BATTERY=CC=CC=A ; F[B-](F)(F)[N+] =CC=[N+]([B-](F)(F)F)A=A </t>
-  </si>
-  <si>
-    <t>B(F)(F)F.INTERFACE STABILITY=CC=CC=B4; F[B-](F)(F)[L+]4=CC=[L+]([B-](F)(F)F)B=B4</t>
   </si>
 </sst>
 </file>
@@ -10730,7 +10715,9 @@
       <c r="I101" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J101" s="3"/>
+      <c r="J101" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="K101" s="3">
         <v>2013</v>
       </c>
@@ -12307,7 +12294,9 @@
       <c r="I133" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="J133" s="3"/>
+      <c r="J133" s="48" t="s">
+        <v>1511</v>
+      </c>
       <c r="K133" s="3">
         <v>2025</v>
       </c>
@@ -14716,7 +14705,9 @@
       <c r="I182" s="3" t="s">
         <v>1368</v>
       </c>
-      <c r="J182" s="3"/>
+      <c r="J182" s="48" t="s">
+        <v>1510</v>
+      </c>
       <c r="K182" s="3">
         <v>2021</v>
       </c>
@@ -15431,6 +15422,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P196" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
